--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0034.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0034.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Default: Akimbo</t>
+          <t>Mặc định: Song súng</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Default: Akimbo</t>
+          <t>Mặc định: Song súng</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Default: Akimbo</t>
+          <t>Mặc định: Song súng</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Default: Akimbo</t>
+          <t>Mặc định: Song súng</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Default: Akimbo</t>
+          <t>Mặc định: Song súng</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Default: Akimbo</t>
+          <t>Mặc định: Song súng</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Please complete the prerequisite quest</t>
+          <t>Hãy hoàn thành nhiệm vụ tiên quyết trước đã</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Geography</t>
+          <t>Địa lý</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>Kinh tế</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Vận chuyển</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Humans và Echo</t>
+          <t>Con người và Tiếng Vọng</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Văn hóa</t>
+          <t>Văn Hóa</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Land</t>
+          <t>Vùng Đất</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Ocean</t>
+          <t>Đại Dương</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Tiêu thụ</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Saving</t>
+          <t>Đang lưu...</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Tự Do</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Regulation</t>
+          <t>Quy Định</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Vehicles</t>
+          <t>Phương Tiện</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Echoes</t>
+          <t>Echo</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Confrontation</t>
+          <t>Đối Đầu</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Coexistence</t>
+          <t>Sự Chung Sống</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Plays</t>
+          <t>Diễn</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Festivities</t>
+          <t>Lễ hội</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Riccioli Islands</t>
+          <t>Quần Đảo Riccioli</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Rinascita: Riccioli Islands</t>
+          <t>Rinascita: Quần Đảo Riccioli</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Rinascita: Averardo Vault</t>
+          <t>Rinascita: Hầm Averardo</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Even When Divinity Remains Silent</t>
+          <t>Dẫu Khi Thần Linh Im Lặng</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Ngôi Sao Hành Hương Xa</t>
+          <t>Ngôi Sao Viễn Du</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Chương III Act III</t>
+          <t>Chương III Hồi III</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Chương III Act IV</t>
+          <t>Chương III Hồi IV</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Ánh Sao Từ Ngày Qua</t>
+          <t>Ánh Sao Ngày Xưa</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Chương III Act V</t>
+          <t>Chương III Hồi V</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Absorb 2 Echoes</t>
+          <t>Hấp thụ 2 Echo.</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Character Enhancement</t>
+          <t>Nâng cấp Nhân vật</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Frostlands Surface</t>
+          <t>Bề Mặt Vùng Băng Giá</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Kích hoạt Chỉ số Phụ mới</t>
+          <t>Kích hoạt Thuộc Tính Phụ Mới</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Current route</t>
+          <t>Lộ trình hiện tại</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Custom Markers</t>
+          <t>Các Biểu Tượng Tùy Chỉnh</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Glacio resistance</t>
+          <t>Kháng Glacio</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Glacio resistance</t>
+          <t>Kháng Glacio</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Fusion resistance</t>
+          <t>Kháng Fusion</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Fusion resistance</t>
+          <t>Kháng Fusion</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Electro resistance</t>
+          <t>Kháng Điện</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Electro resistance</t>
+          <t>Kháng Điện</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Aero resistance</t>
+          <t>Kháng Aero</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Aero resistance</t>
+          <t>Kháng Aero</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Spectro resistance</t>
+          <t>Kháng Phổ Quang</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Spectro resistance</t>
+          <t>Kháng Phổ Quang</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Havoc resistance</t>
+          <t>Kháng Hỗn Loạn</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Havoc resistance</t>
+          <t>Kháng Hỗn Loạn</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>HP Enhancement</t>
+          <t>Cường Hóa HP</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>HP Enhancement</t>
+          <t>Cường Hóa HP</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>ATK Enhancement</t>
+          <t>Tăng ATK</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>ATK Enhancement</t>
+          <t>Tăng ATK</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>ATK Enhancement</t>
+          <t>Tăng ATK</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Top Drive Track</t>
+          <t>Đường Đua Đỉnh Cao</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Navigation Unit</t>
+          <t>Bộ phận Định vị</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Power Mô-đun</t>
+          <t>Mô-đun Năng Lượng</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Top Drive Track</t>
+          <t>Đường Đua Đỉnh Cao</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Top Drive Track</t>
+          <t>Đường Đua Đỉnh Cao</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Navigation Unit</t>
+          <t>Bộ phận Định vị</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Power Mô-đun</t>
+          <t>Mô-đun Năng Lượng</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Top Drive Track</t>
+          <t>Đường Đua Đỉnh Cao</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Navigation Unit</t>
+          <t>Bộ phận Định vị</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Power Mô-đun</t>
+          <t>Mô-đun Năng Lượng</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Top Drive Track</t>
+          <t>Đường Đua Đỉnh Cao</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Navigation Unit</t>
+          <t>Bộ phận Định vị</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Power Mô-đun</t>
+          <t>Mô-đun Năng Lượng</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Top Drive Track</t>
+          <t>Đường Đua Đỉnh Cao</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Navigation Unit</t>
+          <t>Bộ phận Định vị</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Navigation Unit</t>
+          <t>Bộ phận Định vị</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Power Mô-đun</t>
+          <t>Mô-đun Năng Lượng</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Top Drive Track</t>
+          <t>Đường Đua Đỉnh Cao</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Navigation Unit</t>
+          <t>Bộ phận Định vị</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Power Mô-đun</t>
+          <t>Mô-đun Năng Lượng</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Top Drive Track</t>
+          <t>Đường Đua Đỉnh Cao</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Navigation Unit</t>
+          <t>Bộ phận Định vị</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Power Mô-đun</t>
+          <t>Mô-đun Năng Lượng</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Power Mô-đun</t>
+          <t>Mô-đun Năng Lượng</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Surface Layer</t>
+          <t>Bề Mặt</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Relay Layer</t>
+          <t>Lớp Trung Chuyển</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Deep Layer</t>
+          <t>Tầng Sâu</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Mutation Layer</t>
+          <t>Lớp Đột Biến</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Tomorrow</t>
+          <t>Ngày mai</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2 ngày sau</t>
+          <t>2 Ngày Sau</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Medium Tacet Field - Transmitter</t>
+          <t>Tổ Tacet Cỡ Trung - Bộ Truyền Tín</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Medium Tacet Field - Vũ khí</t>
+          <t>Tổ Tacet Cỡ Trung - Vũ Khí</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Medium Tacet Field - Echo</t>
+          <t>Tổ Tacet Cấp Trung - Echo</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Medium Tacet Field - Tacetite</t>
+          <t>Tổ Tacet Cấp Trung - Tacetite</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Mutant Organism</t>
+          <t>Sinh vật thể đột biến</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Con người</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Discord</t>
+          <t>Tacet Discord</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Major Tacet Field</t>
+          <t>Tổ Tacet Chính</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Illusive Realm</t>
+          <t>Cõi Ảo Ảnh</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>EXP Materials</t>
+          <t>Nguyên liệu Kinh Nghiệm</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Simulation Challenge</t>
+          <t>Thử Thách Mô Phỏng</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Vật liệu Thăng hoa Resonator</t>
+          <t>Nguyên Liệu Thăng Cấp Resonator</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Thử thách Boss</t>
+          <t>Thử Thách Trùm</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Echo Materials</t>
+          <t>Vật liệu Echo</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Tacet Suppression</t>
+          <t>Đàn Áp Tacet</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Nightmare</t>
+          <t>Ác Mộng</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Calamity Class</t>
+          <t>Hạng Thảm Họa</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Forgery Challenge</t>
+          <t>Thử Thách Giả Tạo</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Hologram Chiến Thuật</t>
+          <t>Bản Hologram Chiến Thuật</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Resonator Combat Training</t>
+          <t>Huấn Luyện Chiến Đấu Resonator</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Medium Tacet Field</t>
+          <t>Tổ Tacet Cỡ Trung</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Large Tacet Field (Abandoned)</t>
+          <t>Tổ Tacet cỡ lớn (bị bỏ hoang)</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Nightmare Purification</t>
+          <t>Thanh Tẩy Ác Mộng</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Nightmares Echoes</t>
+          <t>Tiếng Vọng Ác Mộng</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Discount:</t>
+          <t>Giảm giá:</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Available Until:</t>
+          <t>Thời hạn mở đến:</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Available Until:</t>
+          <t>Thời hạn mở đến:</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Hiệu ứng Concerto: Hòa Tấu</t>
+          <t>Hiệu Ứng Giao Hưởng: Hòa Tấu</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Concerto Effect: Unison</t>
+          <t>Hiệu Ứng Giao Hưởng: Đồng Thanh</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Hiệu Ứng Concerto: Legato</t>
+          <t>Hiệu Ứng Giao Hưởng: Liên Tiết</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Vật Lý</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Fusion</t>
+          <t>Hợp Nhất</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Glacio Harmony</t>
+          <t>Hòa Âm Glacio</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Cold and Hot Ensemble</t>
+          <t>Lạnh... và hơi thở đứt quãng?! Đ-Đừng lại gần tôi! T-tiền công của anh đây.</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>combined heat and power (physics)</t>
+          <t>kết hợp nhiệt và điện (vật lý)</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>thermoelectric ensemble</t>
+          <t>Bộ hợp tấu nhiệt điện</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>air-cooled ensemble (music)</t>
+          <t>bản hòa tấu mát lành (âm nhạc)</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>air-heat ensemble</t>
+          <t>bản hòa tấu nóng bỏng</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Electrical Ensemble</t>
+          <t>Hòa Tấu Điện</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Glacio Extension</t>
+          <t>Kéo Dài Glacio</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Fusion Extension</t>
+          <t>Mở Rộng Hợp Thể</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Electro Extension</t>
+          <t>Mở Rộng Electro</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Aero Extension</t>
+          <t>Kéo Dài Gió</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Spectro Unison</t>
+          <t>Hòa Âm Phổ Quang</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Glacio continuo</t>
+          <t>Âm hưởng Glacio</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Fusion Continuous</t>
+          <t>Hợp Thể Liên Tục</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Electro continuo</t>
+          <t>Điện Liên Tục</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Aero Continuous</t>
+          <t>Aero Liên tục</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>duplex</t>
+          <t>song công</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Bạn đã thu thập hết Supply Chest trong khu vực này.</t>
+          <t>Bạn đã thu thập hết Rương Cung Cấp trong khu vực này.</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Không Supply Chest found</t>
+          <t>Không tìm thấy Rương Cung Cấp nào</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Cannot be used in battle</t>
+          <t>Không thể sử dụng trong trận chiến</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Exploration Rewards Locked</t>
+          <t>Phần Thưởng Thám Hiểm Bị Khóa</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Rương Cung Cấp</t>
+          <t>Supply Chest</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Sonance Casket</t>
+          <t>Hòm Thanh Âm</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Viewpoint</t>
+          <t>Góc nhìn</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Blobfly</t>
+          <t>Ruồi Bóng</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Legend: Leviathan Loyalist</t>
+          <t>Truyền thuyết: Kẻ Trung Thành Leviathan</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Area Quests</t>
+          <t>Nhiệm vụ khu vực</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Windchimer</t>
+          <t>Thú Gió</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Frostbug</t>
+          <t>Bọ Sương</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Thử thách Chiến thuật của Yhoran</t>
+          <t>Thử Thách Chiến Thuật Yhoran</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Công cụ "Casket Sonar" is recommended</t>
+          <t>Gợi ý sử dụng tiện ích "Casket Sonar"</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Công cụ "Lootmapper" is recommended</t>
+          <t>Gợi ý sử dụng tiện ích "Lootmapper"</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Currently unavailable</t>
+          <t>Hiện chưa khả dụng</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Gadgetpod</t>
+          <t>Hộp Công Cụ</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Grapple</t>
+          <t>Móc Câu</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Levitator</t>
+          <t>Thiết bị điều khiển bay</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Cảm Biến</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Wall Dash</t>
+          <t>Đột Kích Tường</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Glider</t>
+          <t>Dù lượn</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Projector</t>
+          <t>Bộ chiếu</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Memo</t>
+          <t>Ghi chú</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Máy quay</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Waypoint</t>
+          <t>Điểm Dẫn Đường</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Casket Sonar</t>
+          <t>Siêu Âm Quan Tài</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Lootmapper</t>
+          <t>Bản Đồ Tài Nguyên</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Hoverdroid: Shooter</t>
+          <t>Robot Bay Lượn: Bộ phận bắn</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Flight</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Chưa có Sonata Effect</t>
+          <t>Chưa có Hiệu Ứng Sonata</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Chỉ Resonators thuộc hệ Hỏa mới có thể tham gia trận chiến này.</t>
+          <t>Chỉ Resonator thuộc hệ Hỏa mới có thể tham gia trận chiến này.</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Choral Atlas</t>
+          <t>Bản Đồ Hợp Ca</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Choral Atlas</t>
+          <t>Bản Đồ Hợp Ca</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Mức độ đe dọa</t>
+          <t>Mức Đe Dọa</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Loại Tacet Field</t>
+          <t>Loại Tổ Tacet</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Nhận Material</t>
+          <t>Nhận Vật Liệu</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Recipe</t>
+          <t>Công thức</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Dish Type</t>
+          <t>Loại Món</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Decoction Formula</t>
+          <t>Công thức Độc Dược</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Construction Formula</t>
+          <t>Công Thức Xây Dựng</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Mức độ đe dọa</t>
+          <t>Mức Đe Dọa</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Attribute</t>
+          <t>Thuộc tính</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Owned</t>
+          <t>Đã sở hữu</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Danh mục</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Catch Bampuff</t>
+          <t>Bắt Bampuff</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Get Palm Tree Log</t>
+          <t>Nhận Thân Cây Dừa</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Catch Til the Fin-ish</t>
+          <t>Bắt Til the Fin-ish</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Discard</t>
+          <t>Hủy Bỏ</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Attribute</t>
+          <t>Thuộc tính</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Đặt</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Attribute</t>
+          <t>Thuộc tính</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Attribute</t>
+          <t>Thuộc tính</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Rewards Vượt ải lần đầu</t>
+          <t>Phần Thưởng Lần Đầu Vượt Ải</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Legend: Devourer of Greed</t>
+          <t>Truyền thuyết: Kẻ Thôn Tính Tham Lam</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Legend: Mackerel Gear</t>
+          <t>Truyền thuyết: Bánh Răng Cá Thu</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Legend: Pink Relic</t>
+          <t>Truyền thuyết: Di Vật Hồng</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Huyền Thoại Night: Harbinger Của Imperator</t>
+          <t>Huyền Thoại Đêm: Sứ Giả Của Imperator</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Huyền Thoại Night: Tiếng Gọi Của Chúa Tể</t>
+          <t>Huyền Thoại Đêm: Tiếng Gọi Của Chúa Tể</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Huyền Thoại Night: Kẻ Sống Sót Qua Thời Gian</t>
+          <t>Huyền Thoại Đêm: Kẻ Sống Sót Qua Thời Gian</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Ahab's Request: Maiden Voyage</t>
+          <t>Yêu cầu của Ahab: Chuyến Hải Hành Đầu Tiên</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Ahab's Request: Big Catch</t>
+          <t>Yêu cầu của Ahab: Mẻ Cá Lớn</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Flying Fish, Diving Dragon</t>
+          <t>Cá bay, Rồng lặn</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Special: Offshore Operation</t>
+          <t>Đặc biệt: Chiến dịch Ngoài Khơi</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Special: Silver Flash</t>
+          <t>Đặc biệt: Ánh Chớp Bạc</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Night Special: Jelly Rumpus</t>
+          <t>Đặc Biệt Đêm: Cuộc Vui Sôi Động Của Thạch</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Night Special: Deep Sea Operation</t>
+          <t>Đặc Biệt Đêm: Chiến Dịch Biển Sâu</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Special: One Last Tear</t>
+          <t>Đặc biệt: Giọt Lệ Cuối Cùng</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Speical: Tear-soaked Yarn</t>
+          <t>Đặc Biệt: Sợi Len Ngấm Lệ</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Night Special: Abyssal Mutants</t>
+          <t>Đặc Biệt Đêm: Quái Vật Vực Sâu</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Night Special: Fried Egg Deluxe</t>
+          <t>Đặc Biệt Đêm: Trứng Rán Cao Cấp</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Special: Levioso</t>
+          <t>Đặc biệt: Levioso</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Special: Mở Sea Operation</t>
+          <t>Đặc biệt: Chiến dịch Biển Khơi</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Special: Dazzle Razzle</t>
+          <t>Đặc biệt: Dazzle Razzle</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Special: Horn of Hunters</t>
+          <t>Đặc biệt: Horn of Hunters</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Special: Sunset</t>
+          <t>Đặc biệt: Hoàng Hôn</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Special: Tempera Watercolors</t>
+          <t>Đặc biệt: Tempera Watercolors</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Special: Skilled Hunter</t>
+          <t>Đặc biệt: Thợ Săn Lão Luyện</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Challenge: Sail Across the Sky</t>
+          <t>Thử Thách: Cánh Buồm Lướt Trên Trời</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Challenge Night: Jelly Party</t>
+          <t>Thử Thách Đêm: Bữa Tiệc Sứa</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Challenge: Octopus in the Clam</t>
+          <t>Thử Thách: Bạch Tuộc Trong Vỏ Sò</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Challenge: Yearn for Yarn</t>
+          <t>Thử Thách: Khát Khao Cuộn Len</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Challenge: Đánh Chuông Hay Không Đánh?</t>
+          <t>Thử Thách: Đánh Chuông Hay Không Đánh?</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Challenge: Dragon Bay Cao</t>
+          <t>Thử Thách: Rồng Bay Cao</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Challenge Night: Mềm Mại Hơn Nữa</t>
+          <t>Thử Thách Đêm: Mềm Mại Hơn Nữa</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Challenge: Tricksters</t>
+          <t>Thử Thách: Những Kẻ Lừa Lọc</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Challenge: Đến Khi Chết Mới Chia Tay</t>
+          <t>Thử Thách: Đến Khi Chết Mới Chia Tay</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Challenge: Dumbo Mambo</t>
+          <t>Thử Thách: Vũ Điệu Dumbo</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Challenge: Swallow 'Em Tất cả</t>
+          <t>Thử Thách: Nuốt Chửng Tất Cả</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Challenge: Sob in the Sea</t>
+          <t>Thử Thách: Nức Nở Trong Đại Dương</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Challenge Night: Song Hùng Goober</t>
+          <t>Thử Thách Đêm: Song Hùng Goober</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Challenge: Không Avoiding Foes</t>
+          <t>Thử Thách: Không Thể Tránh Né Kẻ Thù</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Challenge: The Introverts</t>
+          <t>Thử Thách: Những Kẻ Khép Mình</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Challenge Night: Vung Kiếm Nhanh</t>
+          <t>Thử Thách Đêm: Vung Kiếm Nhanh</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Challenge: Sea Angel</t>
+          <t>Thử Thách: Thiên Thần Biển Cả</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Challenge: Feather in Bloom</t>
+          <t>Thử Thách: Cánh Hoa Nở</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Challenge Night: Đi Phà Cùng Bóng Ma</t>
+          <t>Thử Thách Đêm: Đi Phà Cùng Bóng Ma</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Challenge: Snowy Trail</t>
+          <t>Thử Thách: Con Đường Tuyết Trắng</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Challenge Night: Không Mạo Hiểm, Không Thành Công</t>
+          <t>Thử Thách Đêm: Không Mạo Hiểm, Không Thành Công</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Challenge: Ephemeral Bubble</t>
+          <t>Thử Thách: Bong Bóng Phù Du</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Challenge Night: Bẫy Giảm Tốc</t>
+          <t>Thử Thách Đêm: Bẫy Giảm Tốc</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Challenge: Angels in Snow</t>
+          <t>Thách đấu: Angels in Snow</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Challenge: Ancient Ones</t>
+          <t>Thách đấu: Ancient Ones</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Challenge: Wild Hunt</t>
+          <t>Thử Thách: Săn Bắt Hoang Dã</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Challenge: Grievers of the Deep</t>
+          <t>Thử Thách: Những Kẻ Than Khóc Vực Sâu</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Challenge: Sunrise Ló Rạng</t>
+          <t>Thử Thách: Bình Minh Ló Rạng</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Challenge: Predator and Prey</t>
+          <t>Thử Thách: Thú Săn Mồi Và Con Mồi</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Challenge Night: Thợ Săn Astrite</t>
+          <t>Thử Thách Đêm: Astrite Hunter</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Challenge: The Strongest Shape</t>
+          <t>Thử Thách: Hình Dạng Mạnh Nhất</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Challenge Night: Cương Duyên Thủy Thần</t>
+          <t>Thử Thách Đêm: Cương Duyên Thủy Thần</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Challenge: The Solar Surveyor</t>
+          <t>Thử Thách: Nhà Thám Hiểm Mặt Trời</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Challenge Night: Cua và Tôm</t>
+          <t>Thử Thách Đêm: Cua và Tôm</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Challenge Night: Vươn Tới Ngôi Sao</t>
+          <t>Thử Thách Đêm: Vươn Tới Ngôi Sao</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Đi bắt cá</t>
+          <t>Đi bắt vài con cá nào</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Cute Ocean Dwellers</t>
+          <t>Những Cư Dân Dễ Thương Dưới Đại Dương</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Take a Giant Gulp</t>
+          <t>Uống Một Ngụm Lớn Đi</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Prickly Pugilist</t>
+          <t>Đấu Sĩ Gai Góc</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Night Fishing: Goofy Goober</t>
+          <t>Câu Cá Đêm: Chú Cá Ngốc Nghếch</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Ahab's Request: Find the Key</t>
+          <t>Yêu cầu của Ahab: Tìm Chìa Khóa</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Ahab's Request: Rainbow Rush</t>
+          <t>Yêu cầu của Ahab: Cơn Sóng Cầu Vồng</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Ahab's Request: Rainbow Rush</t>
+          <t>Yêu cầu của Ahab: Cơn Sóng Cầu Vồng</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Ahab's Request: Mackerel Gear</t>
+          <t>Yêu cầu của Ahab: Dụng Cụ Câu Cá Thu</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Lancet of the Sea</t>
+          <t>Lưỡi Kiếm Đại Dương</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Sound of Trombone</t>
+          <t>Âm thanh kèn Trombone</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>To the Farthest Horizon</t>
+          <t>Tới Chân Trời Xa Nhất</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Jelly Party</t>
+          <t>Bữa Tiệc Sứa</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Sail Across the Sky</t>
+          <t>Vượt Biển Trời Xanh</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Mimicry</t>
+          <t>Bắt Chước</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Yearn for Yarn</t>
+          <t>Khao Khát Cuộn Len</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Sail Across the Sky</t>
+          <t>Vượt Biển Trời Xanh</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Til Death Do Us Part</t>
+          <t>Đến Khi Chết Cách Xa</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Mimicry</t>
+          <t>Bắt Chước</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Yearn for Yarn</t>
+          <t>Khao Khát Cuộn Len</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Múa Cá Dragon</t>
+          <t>Múa Cá Rồng</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Night Fishing: Yum Yum</t>
+          <t>Câu Cá Đêm: Ngon Tuyệt</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Night Fishing: Kẻ Săn Mồi Dịu Dàng</t>
+          <t>Câu Cá Đêm: Kẻ Săn Mồi Dịu Dàng</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Swallow 'Em Tất cả</t>
+          <t>Nuốt Chửng Tất Cả</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Night Fishing: Luminous Night</t>
+          <t>Câu Cá Đêm: Luminous Night</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Sob in the Sea</t>
+          <t>Nước mắt giữa biển khơi</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Night Fishing: Luminous Night</t>
+          <t>Câu Cá Đêm: Luminous Night</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Sob in the Sea</t>
+          <t>Nước mắt giữa biển khơi</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Night Fishing: Double Goober</t>
+          <t>Câu Cá Đêm: Song Ngư Bự Con</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Night Fishing: Light Trong Lòng Vực</t>
+          <t>Câu Cá Đêm: Ánh Sáng Trong Lòng Vực</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Lonely Blob</t>
+          <t>Khối Cô Đơn</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Fly Dumbo Fly</t>
+          <t>Bay lên nào Dumbo</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Night Fishing: Goofystar</t>
+          <t>Câu Cá Đêm: Ngôi Sao Ngốc Nghếch</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Night Fishing: Cuteness Aggression</t>
+          <t>Câu Cá Đêm: Dễ Thương Đến Phát Sợ</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Night Fishing: What's Salp, Crab</t>
+          <t>Câu Cá Đêm: Salp Hay Cua Đây?</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Sea Angel</t>
+          <t>Thiên Sứ Biển</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Night Fishing: Đi Phà Cùng Bóng Ma</t>
+          <t>Câu Cá Đêm: Đi Phà Cùng Bóng Ma</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Gaze from the Dead</t>
+          <t>Ánh Nhìn Từ Cõi Chết</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Snowy Trail</t>
+          <t>Lối Tuyết</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Night Fishing: Người Bảo Vệ Phantom</t>
+          <t>Câu Cá Đêm: Người Bảo Vệ Ảo Ảnh</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Gaze from the Dead</t>
+          <t>Ánh Nhìn Từ Cõi Chết</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Night Fishing: Nothing Ventured</t>
+          <t>Câu Cá Đêm: Không Mạo Hiểm, Không Thành Công</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Sea of Feathers</t>
+          <t>Biển Lông Vũ</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Night Fishing: Everhaunting Phantom</t>
+          <t>Câu Cá Đêm: Bóng Ma Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>The Restless Eye</t>
+          <t>Con Mắt Bất An</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Iron Lady</t>
+          <t>Quý Bà Thép</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Nigh Fishing: Snow-covered Trap</t>
+          <t>Câu Cá Gần Đêm: Bẫy Tuyết Phủ</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Night Fishing: Lơ Lửng Và Lóe Sáng</t>
+          <t>Câu Cá Đêm: Lơ Lửng Và Lóe Sáng</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Night Fishing: Trong Đại Sảnh Vực Sâu</t>
+          <t>Câu Cá Đêm: Trong Đại Sảnh Vực Sâu</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Sunrise</t>
+          <t>Bình Minh</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Red Horned Mobile Suit</t>
+          <t>Khung Cơ Động Sừng Đỏ</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>The Strongest Shape</t>
+          <t>Hình Thể Tối Thượng</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>The Hermit of Legends</t>
+          <t>Ẩn Sĩ Huyền Thoại</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Red Horned Mobile Suit</t>
+          <t>Khung Cơ Động Sừng Đỏ</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>The Strongest Shape</t>
+          <t>Hình Thể Tối Thượng</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Night Fishing: Dây Cương Của Thần Biển</t>
+          <t>Câu Cá Đêm: Dây Cương Của Thần Biển</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Prey or Predator</t>
+          <t>Con mồi hay Kẻ săn mồi</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Triangulation</t>
+          <t>Định vị tam giác</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Extinction Event</t>
+          <t>Sự Kiện Tuyệt Chủng</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Sun Above the Tripod</t>
+          <t>Mặt Trời Trên Đài Tam Túc</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Bảng màu</t>
+          <t>Bảng Màu</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Predator and Hermit</t>
+          <t>Thợ Săn và Ẩn Sĩ</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Catch Coconut Urchin</t>
+          <t>Bắt Nhím Dừa</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Get Riccioli Black Pearl</t>
+          <t>Lấy Hạt Ngọc Đen Riccioli</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Get Coast Flax</t>
+          <t>Nhận Cây Gai Bờ Biển</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Get Metal Debris</t>
+          <t>Nhận Mảnh Kim Loại</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Catch Octopus Clam</t>
+          <t>Bắt Sò Bạch Tuộc</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Catch Bell-less Crab</t>
+          <t>Bắt Cua Không Chuông</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Catch Airsailer</t>
+          <t>Bắt Airsailer</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Catch Fried Egg Jellyfish</t>
+          <t>Bắt Sứa Trứng Rán</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Catch Leafy Seadragon</t>
+          <t>Bắt Cá Rồng Lá</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Catch Yarn Eel</t>
+          <t>Bắt Lươn Len</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Catch Dumbo Octopus</t>
+          <t>Bắt Bạch Tuộc Dumbo</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Catch Giant Gulper</t>
+          <t>Bắt Cá Hố Khổng Lồ</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Catch Sob Blob</t>
+          <t>Bắt Sob Blob</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Catch Gooberstar</t>
+          <t>Bắt Sao Goober</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Catch Pricklecrab</t>
+          <t>Bắt Cua Gai</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Catch Clione</t>
+          <t>Bắt Bướm Biển</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Catch Feather Star</t>
+          <t>Bắt Sao Biển Lông Vũ</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Catch Stygian Phantom</t>
+          <t>Bắt Hồn Ma Stygian</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Catch Seabed Snow</t>
+          <t>Bắt Tuyết Dưới Đáy Biển</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Catch Trapper Anglerfish</t>
+          <t>Bắt Cá Mút Trapper</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Catch Titanium Mackerel</t>
+          <t>Bắt Cá Thu Titanium</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Catch Bubble Snail</t>
+          <t>Bắt Ốc Bong Bóng</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Catch Sunfish</t>
+          <t>Bắt Cá Mặt Trời</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Catch Legilimens Shrimp</t>
+          <t>Bắt Tôm Thần Nhãn</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Catch Lancetfish</t>
+          <t>Bắt Cá Kiếm</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Catch Tripod Fish</t>
+          <t>Bắt Cá Ba Chân</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Catch Trombone Ammonoid</t>
+          <t>Bắt Ốc Trombone</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Catch Reinfish</t>
+          <t>Bắt Cá Reinfish</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Catch Pink Hallowfin</t>
+          <t>Bắt Cá Hồng Halowfin</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Catch Pelagic Wyrm</t>
+          <t>Bắt Giun Biển Khơi</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Catch Overlord Squid</t>
+          <t>Bắt Mực Chúa Tể</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Catch Bogie Shrimp</t>
+          <t>Bắt Tôm Bóng Ma</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Catch Coconut Urchin Mutant</t>
+          <t>Bắt Nhím Dừa Đột Biến</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Catch Bell-less Crab Mutant</t>
+          <t>Bắt Cua Không Chuông Đột Biến</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Catch Airsailer Mutant</t>
+          <t>Bắt Airsailer Đột Biến</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Catch Fried Egg Jellyfish Mutant</t>
+          <t>Bắt Sứa Trứng Rán Đột Biến</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Catch Leafy Seadragon Mutant</t>
+          <t>Bắt Biến Thể Cá Rồng Lá</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Catch Yarn Eel Mutant</t>
+          <t>Bắt Lươn Len Đột Biến</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Catch Dumbo Octopus Mutant</t>
+          <t>Bắt Bạch Tuộc Dumbo Đột Biến</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Catch Salp Mutant</t>
+          <t>Bắt Sứa Salp Đột Biến</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Catch Sob Blob Mutant</t>
+          <t>Bắt Biến Thể Sob Blob</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Catch Pokey Moray Mutant</t>
+          <t>Bắt Cá Moray Gai Nhọn Đột Biến</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Catch Pricklecrab Mutant</t>
+          <t>Bắt Cua Gai Đột Biến</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Catch Clione Mutant</t>
+          <t>Bắt Bướm Biển Đột Biến</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Catch Feather Star Mutant</t>
+          <t>Bắt Sao Biển Lông Vũ Đột Biến</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Catch Dead Man's Eye Mutant</t>
+          <t>Bắt Mắt Người Chết Đột Biến</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Catch Seabed Snow Mutant</t>
+          <t>Bắt Biến Thể Tuyết Dưới Đáy Biển</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Catch Trapper Anglerfish Mutant</t>
+          <t>Bắt Biến Thể Cá Mút Trapper</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Catch Sunfish Mutant</t>
+          <t>Bắt Biến Thể Cá Mặt Trời</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Catch Legilimens Shrimp Mutant</t>
+          <t>Bắt Biến Thể Tôm Thần Nhãn</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Catch Lancetfish Mutant</t>
+          <t>Bắt Biến Thể Cá Giò Lancet</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Catch Tripod Fish Mutant</t>
+          <t>Bắt Cá Ba Chân Đột Biến</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Catch Rainbow Dolphinfish Mutant</t>
+          <t>Bắt Cá Chuồn Cầu Vồng Đột Biến</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Catch Trombone Ammonoid Mutant</t>
+          <t>Bắt Ốc Trombone Đột Biến</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Đi bắt cá</t>
+          <t>Đi bắt vài con cá nào</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Không Bell Please</t>
+          <t>Xin đừng rung chuông</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Bắt Cá Vua: Titanium Mackerel</t>
+          <t>Bắt Cá Vua: Cá Thu Titan</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Fish King: Titanium Mackerel</t>
+          <t>Vua Cá: Cá Thu Titan</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Permanent</t>
+          <t>Vĩnh viễn</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>New Recipe Learned</t>
+          <t>Công Thức Mới đã học được</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Triệu Tập</t>
+          <t>Triệu tập</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Co-op Mode</t>
+          <t>Chế độ Đồng Đội</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
